--- a/assets/program_logic_v6.xlsx
+++ b/assets/program_logic_v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7100f48b682a1df6/Work/20251027 IEC TC86 Digital Tool/Digital tool/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="305" documentId="13_ncr:1_{FD3D256E-43A5-4E0A-8438-014B95F3FA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5A7D235-857E-44DF-83DE-1BCFC099A98F}"/>
+  <xr:revisionPtr revIDLastSave="323" documentId="13_ncr:1_{FD3D256E-43A5-4E0A-8438-014B95F3FA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1815D9FC-8649-4E65-BB83-ED83DD186907}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="11" xr2:uid="{0D1380F2-B44E-49CB-9379-F623B51E2EAA}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="3" xr2:uid="{0D1380F2-B44E-49CB-9379-F623B51E2EAA}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="8" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="Filter 2" sheetId="15" r:id="rId10"/>
     <sheet name="Filter 3" sheetId="16" r:id="rId11"/>
     <sheet name="Filter 4" sheetId="19" r:id="rId12"/>
+    <sheet name="Filter 5" sheetId="20" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="123">
   <si>
     <t>Connector type</t>
   </si>
@@ -352,21 +353,6 @@
     <t>IEC 63267-3-1 *d</t>
   </si>
   <si>
-    <t>B (mean ≤ 0,12 dB; at least 97 % ≤ 0,25 dB)</t>
-  </si>
-  <si>
-    <t>C (mean ≤ 0,25 dB; at least 97 % ≤ 0,5 dB)</t>
-  </si>
-  <si>
-    <t>D (mean ≤ 0,5 dB; at least 97% ≤ 1,0 dB)</t>
-  </si>
-  <si>
-    <t>Bm (mean ≤ 0,3 dB; at least 97 % ≤ 0,6 dB)</t>
-  </si>
-  <si>
-    <t>Cm (mean ≤ 0,5 dB; at least 97 % ≤ 1,0 dB)</t>
-  </si>
-  <si>
     <t>Primary coated fibre</t>
   </si>
   <si>
@@ -397,9 +383,6 @@
     <t>Cable type</t>
   </si>
   <si>
-    <t>Mechanical and environmental cable performance (terminated as cable assembly)</t>
-  </si>
-  <si>
     <t>IN1</t>
   </si>
   <si>
@@ -416,6 +399,24 @@
   </si>
   <si>
     <t>IN3</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Bm</t>
+  </si>
+  <si>
+    <t>Cm</t>
+  </si>
+  <si>
+    <t>IN7</t>
+  </si>
+  <si>
+    <t>Mechanical and environmental cable performance</t>
   </si>
 </sst>
 </file>
@@ -1303,7 +1304,7 @@
         <v>54</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1682,13 +1683,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1786,15 +1787,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -1802,7 +1803,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
         <v>45</v>
@@ -1810,7 +1811,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B4" t="s">
         <v>45</v>
@@ -1818,7 +1819,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -1826,7 +1827,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -1848,15 +1849,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -1864,7 +1865,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
@@ -1872,7 +1873,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>4</v>
@@ -1880,7 +1881,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>5</v>
@@ -1888,7 +1889,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
@@ -1896,7 +1897,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>7</v>
@@ -1904,7 +1905,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
@@ -1912,7 +1913,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1920,7 +1921,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -1928,7 +1929,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
@@ -1936,7 +1937,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
@@ -1944,7 +1945,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>3</v>
@@ -1952,7 +1953,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>4</v>
@@ -1960,7 +1961,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>5</v>
@@ -1968,7 +1969,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>6</v>
@@ -1976,7 +1977,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>7</v>
@@ -1984,7 +1985,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>8</v>
@@ -1992,7 +1993,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -2000,7 +2001,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>10</v>
@@ -2008,7 +2009,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>11</v>
@@ -2016,7 +2017,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2</v>
@@ -2024,7 +2025,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>3</v>
@@ -2032,7 +2033,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>4</v>
@@ -2040,7 +2041,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>5</v>
@@ -2048,7 +2049,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>6</v>
@@ -2056,7 +2057,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>7</v>
@@ -2064,7 +2065,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>8</v>
@@ -2072,7 +2073,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -2080,7 +2081,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>10</v>
@@ -2088,7 +2089,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>11</v>
@@ -2096,7 +2097,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>2</v>
@@ -2104,7 +2105,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>3</v>
@@ -2112,7 +2113,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>4</v>
@@ -2120,7 +2121,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>5</v>
@@ -2128,7 +2129,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>6</v>
@@ -2136,7 +2137,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>7</v>
@@ -2144,7 +2145,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>8</v>
@@ -2152,7 +2153,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>9</v>
@@ -2160,7 +2161,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>10</v>
@@ -2168,10 +2169,55 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472902C9-8A32-4DC9-BF83-742F54B9DB58}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2357,7 +2403,7 @@
         <v>45</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2457,22 +2503,22 @@
     <col min="5" max="5" width="59.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -2483,7 +2529,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
@@ -2494,7 +2540,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>4</v>
@@ -2505,7 +2551,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>5</v>
@@ -2516,7 +2562,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
@@ -2527,7 +2573,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>7</v>
@@ -2538,7 +2584,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
@@ -2549,7 +2595,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -2560,7 +2606,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -2571,7 +2617,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
@@ -2582,7 +2628,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
@@ -2593,7 +2639,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>3</v>
@@ -2604,7 +2650,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>4</v>
@@ -2615,7 +2661,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>5</v>
@@ -2626,7 +2672,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>6</v>
@@ -2637,7 +2683,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>7</v>
@@ -2648,7 +2694,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>8</v>
@@ -2659,7 +2705,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -2670,7 +2716,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>10</v>
@@ -2681,7 +2727,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>11</v>
@@ -2692,7 +2738,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2</v>
@@ -2703,7 +2749,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>3</v>
@@ -2714,7 +2760,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>4</v>
@@ -2725,7 +2771,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>5</v>
@@ -2736,7 +2782,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>6</v>
@@ -2747,7 +2793,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>7</v>
@@ -2758,7 +2804,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>8</v>
@@ -2769,7 +2815,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -2780,7 +2826,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>10</v>
@@ -2791,7 +2837,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>11</v>
@@ -2802,7 +2848,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>2</v>
@@ -2813,7 +2859,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>3</v>
@@ -2824,7 +2870,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>4</v>
@@ -2835,51 +2881,51 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>9</v>
@@ -2890,7 +2936,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>10</v>
@@ -2901,7 +2947,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>11</v>
@@ -3400,10 +3446,10 @@
     </row>
     <row r="2" spans="1:2" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3474,13 +3520,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">

--- a/assets/program_logic_v6.xlsx
+++ b/assets/program_logic_v6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7100f48b682a1df6/Work/20251027 IEC TC86 Digital Tool/Digital tool/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="323" documentId="13_ncr:1_{FD3D256E-43A5-4E0A-8438-014B95F3FA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1815D9FC-8649-4E65-BB83-ED83DD186907}"/>
+  <xr:revisionPtr revIDLastSave="399" documentId="13_ncr:1_{FD3D256E-43A5-4E0A-8438-014B95F3FA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17CC27A0-549F-4938-A79E-1CD5CF66B348}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="3" xr2:uid="{0D1380F2-B44E-49CB-9379-F623B51E2EAA}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="12" xr2:uid="{0D1380F2-B44E-49CB-9379-F623B51E2EAA}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="8" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="123">
   <si>
     <t>Connector type</t>
   </si>
@@ -487,12 +487,42 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -507,51 +537,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -893,773 +953,774 @@
   <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="44.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="61.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="13" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="5" t="str">
+      <c r="E2" s="10" t="str">
         <f>D2</f>
         <v>IEC 61755-2-1</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="5" t="str">
+      <c r="E3" s="10" t="str">
         <f t="shared" ref="E3:E28" si="0">D3</f>
         <v>IEC 61755-2-2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="5" t="str">
+      <c r="E4" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 63267-2-1</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="5" t="str">
+      <c r="E5" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-1</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="5" t="str">
+      <c r="E6" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-2</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="5" t="str">
+      <c r="E7" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 63267-2-1</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="5" t="str">
+      <c r="E8" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-1</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="5" t="str">
+      <c r="E9" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-2</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="5" t="str">
+      <c r="E10" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 63267-2-1</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="5" t="str">
+      <c r="E11" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-2</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="5" t="str">
+      <c r="E12" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 63267-2-1</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="10" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="5" t="str">
+      <c r="E13" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-2</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="10" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="5" t="str">
+      <c r="E14" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 63267-2-1</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="10" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="5" t="str">
+      <c r="E15" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not available</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="5" t="str">
+      <c r="E16" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-2</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="5" t="str">
+      <c r="E17" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 63267-2-1</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="10" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="5" t="str">
+      <c r="E18" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-2</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="10" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="5" t="str">
+      <c r="E19" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 63267-2-1</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="10" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="5" t="str">
+      <c r="E20" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-1</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="B21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="5" t="str">
+      <c r="E21" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-2</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="5" t="str">
+      <c r="E22" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 63267-2-1</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="B23" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="5" t="str">
+      <c r="E23" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-1</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="B24" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="5" t="str">
+      <c r="E24" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-2</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="5" t="str">
+      <c r="E25" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 63267-2-1</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="B26" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="5" t="str">
+      <c r="E26" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-1</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B27" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E27" s="5" t="str">
+      <c r="E27" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 61755-2-2</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B28" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="5" t="str">
+      <c r="E28" s="10" t="str">
         <f t="shared" si="0"/>
         <v>IEC 63267-2-1</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1676,99 +1737,100 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1780,56 +1842,57 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="18" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="18" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="18" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1840,338 +1903,259 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF1F731-31FC-468D-A938-C8BAE32CA9F3}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="16" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="21" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="21" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="21" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="21" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="21" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="21" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="3" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="3" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="3" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="3" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>102</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>103</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A31" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>104</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>104</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>104</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>104</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>104</v>
-      </c>
-      <c r="B41" s="3" t="s">
+      <c r="B31" s="21" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2184,39 +2168,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472902C9-8A32-4DC9-BF83-742F54B9DB58}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="12"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="16" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="18" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="18" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="18" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2230,95 +2218,96 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="10" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2335,151 +2324,152 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="71.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="71.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2496,463 +2486,464 @@
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="24" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="24" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="24" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="24" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="24" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="24" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="26" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="26" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="26" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="26" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="26" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="24" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="24" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="24" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2969,95 +2960,96 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="10" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3074,239 +3066,240 @@
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="13" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="B12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="B17" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B19" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B20" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3323,101 +3316,102 @@
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
+      <c r="A5" s="30"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="17"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="29"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="17"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="29"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="17"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="29"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="17"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="17"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="29"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="17"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="29"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="17"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="29"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="17"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="29"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="17"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="29"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
+      <c r="A21" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3432,52 +3426,53 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="92.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="92.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="15" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="9" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="9" t="s">
         <v>87</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -3485,18 +3480,18 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="9" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3513,316 +3508,317 @@
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="16" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="B21" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="B23" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="B24" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="B26" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B27" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B28" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="17" t="s">
         <v>15</v>
       </c>
     </row>

--- a/assets/program_logic_v6.xlsx
+++ b/assets/program_logic_v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7100f48b682a1df6/Work/20251027 IEC TC86 Digital Tool/Digital tool/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7100f48b682a1df6/Work/20251027 IEC TC86 Digital Tool/v3/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="399" documentId="13_ncr:1_{FD3D256E-43A5-4E0A-8438-014B95F3FA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17CC27A0-549F-4938-A79E-1CD5CF66B348}"/>
+  <xr:revisionPtr revIDLastSave="405" documentId="13_ncr:1_{FD3D256E-43A5-4E0A-8438-014B95F3FA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A7B3DF-464B-4946-8342-81C72661BEA4}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="12" xr2:uid="{0D1380F2-B44E-49CB-9379-F623B51E2EAA}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="7" xr2:uid="{0D1380F2-B44E-49CB-9379-F623B51E2EAA}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="8" r:id="rId1"/>
@@ -537,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -548,7 +548,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -594,13 +594,12 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -627,10 +626,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2486,12 +2481,12 @@
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" style="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="22"/>
+    <col min="1" max="1" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2508,10 +2503,10 @@
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="23" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -2519,10 +2514,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -2530,10 +2525,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -2541,10 +2536,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="23" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -2552,10 +2547,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -2563,10 +2558,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -2574,10 +2569,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -2585,10 +2580,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -2596,10 +2591,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -2607,10 +2602,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -2618,10 +2613,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="23" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -2629,10 +2624,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -2640,10 +2635,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="23" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -2651,54 +2646,54 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -2706,10 +2701,10 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="23" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -2717,10 +2712,10 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -2728,222 +2723,222 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="23" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="23" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="25" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="25" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="25" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="25" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="25" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="23" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="23" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="23" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3348,70 +3343,70 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
+      <c r="A5" s="29"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="29"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="29"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="29"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
+      <c r="A21" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
